--- a/examples/dirty-keys-demo.xlsx
+++ b/examples/dirty-keys-demo.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>действие 4 обрезает края</t>
+          <t>края чистятся ВСЕГДА, при любых флажках</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
     <row r="25" hidden="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Скрытая строка - пропускается</t>
+          <t>Скрытая строка - тоже чистится</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -958,19 +958,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XX.U1.ABС.0009</t>
+          <t>XX.U1.ABC.0009</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>строка скрыта; попадёт в счётчик скрытых</t>
+          <t>строка скрыта; в отчёте будет посчитана как скрытая</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Разное оформление символов - пропускается</t>
+          <t>Разное оформление символов - чистится, оформление сохраняется</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>XX.U1.ABС.0011</t>
+          <t>XX.U1.ABC.0011</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>первая буква жирная; попадёт в счётчик</t>
+          <t>первая буква жирная и останется жирной</t>
         </is>
       </c>
     </row>
